--- a/data/UserManger/update_user_status.xlsx
+++ b/data/UserManger/update_user_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15960" windowHeight="9870" activeTab="1"/>
+    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
   <si>
     <t>allureEpic</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>assert</t>
-  </si>
-  <si>
-    <t>sql</t>
   </si>
   <si>
     <t>update_user_status_01</t>
@@ -1211,7 +1208,7 @@
     <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="9" width="5.625" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="7.25" customWidth="1"/>
+    <col min="11" max="11" width="8.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1252,292 +1249,290 @@
       <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="M1" s="1"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" ht="41" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="M2" s="4"/>
     </row>
     <row r="3" ht="51" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M3" s="4"/>
     </row>
     <row r="4" ht="51" customHeight="1" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M4" s="4"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" s="4"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="F7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M8" s="4"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
       <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M9" s="4"/>
     </row>

--- a/data/UserManger/update_user_status.xlsx
+++ b/data/UserManger/update_user_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="53">
   <si>
     <t>allureEpic</t>
   </si>
@@ -95,7 +95,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>[{'case_id': 'create_user_03', 'dependent_data': [{'dependent_type': 'response', 'jsonpath': '$.data.id', 'set_cache': 'id', 'replace_key': None}]}]</t>
+    <t>[{'case_id': 'create_user_01', 'dependent_data': [{'dependent_type': 'response', 'jsonpath': '$.data.id', 'set_cache': 'id', 'replace_key': None}]}]</t>
   </si>
   <si>
     <t>{'errorInfo_1': {'jsonpath': '$.data.mg_state', 'type': '==', 'value': 1, 'AssertType': None}, 'errorInfo_2': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '设置状态成功', 'AssertType': None}, 'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 200, 'AssertType': None}}</t>
@@ -1155,11 +1155,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="22.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="15.6296296296296" customWidth="1"/>
+    <col min="3" max="3" width="18.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1196,17 +1196,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
-    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="1" max="1" width="14.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="16.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.6296296296296" customWidth="1"/>
     <col min="5" max="5" width="25.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="9" max="9" width="5.625" customWidth="1"/>
+    <col min="7" max="7" width="12.3796296296296" customWidth="1"/>
+    <col min="8" max="8" width="12.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="5.62962962962963" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="8.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
@@ -1313,9 +1313,7 @@
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="4"/>
       <c r="J3" s="3" t="s">
         <v>31</v>

--- a/data/UserManger/update_user_status.xlsx
+++ b/data/UserManger/update_user_status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9300" activeTab="1"/>
+    <workbookView windowWidth="15960" windowHeight="9870" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -1155,11 +1155,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8796296296296" customWidth="1"/>
-    <col min="2" max="2" width="15.6296296296296" customWidth="1"/>
-    <col min="3" max="3" width="18.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="22.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1196,17 +1196,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="16.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.6296296296296" customWidth="1"/>
+    <col min="4" max="4" width="10.6333333333333" customWidth="1"/>
     <col min="5" max="5" width="25.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="12.3796296296296" customWidth="1"/>
-    <col min="8" max="8" width="12.6296296296296" customWidth="1"/>
-    <col min="9" max="9" width="5.62962962962963" customWidth="1"/>
+    <col min="7" max="7" width="12.3833333333333" customWidth="1"/>
+    <col min="8" max="8" width="12.6333333333333" customWidth="1"/>
+    <col min="9" max="9" width="5.63333333333333" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="8.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
